--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/may-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/may-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC may-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC may-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11777,7 +11777,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12326,7 +12326,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/may-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/may-2025.xlsx
@@ -562,7 +562,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1176,7 +1196,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1261,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1326,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1391,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1456,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1521,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1586,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1651,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1716,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1725,7 +1781,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1846,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1847,7 +1911,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1908,7 +1976,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2041,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2106,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2091,7 +2171,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2236,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2301,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2274,7 +2366,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2431,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2496,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2561,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2626,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2752,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2817,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2882,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2947,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3073,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3006,7 +3138,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3203,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3268,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3333,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3372,7 +3520,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3433,7 +3585,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3650,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3715,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3780,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3845,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3921,7 +4093,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3982,7 +4158,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4223,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4288,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4353,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4226,7 +4418,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4287,7 +4483,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4348,7 +4548,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4409,7 +4613,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4470,7 +4678,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4531,7 +4743,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4592,7 +4808,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4653,7 +4873,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4775,7 +4999,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4836,7 +5064,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4897,7 +5129,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5080,7 +5316,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5141,7 +5381,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5202,7 +5446,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5324,7 +5572,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5385,7 +5637,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5568,7 +5824,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5690,7 +5950,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5751,7 +6015,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +6141,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5934,7 +6206,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6332,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6117,7 +6397,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6178,7 +6462,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6239,7 +6527,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6300,7 +6592,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6422,7 +6718,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6544,7 +6844,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6605,7 +6909,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6666,7 +6974,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6727,7 +7039,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6788,7 +7104,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6849,7 +7169,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6971,7 +7295,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7032,7 +7360,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7215,7 +7547,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7337,7 +7673,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7398,7 +7738,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7864,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7581,7 +7929,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7703,7 +8055,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7764,7 +8120,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7825,7 +8185,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7886,7 +8250,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8008,7 +8376,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8069,7 +8441,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8130,7 +8506,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8191,7 +8571,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8313,7 +8697,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8496,7 +8884,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8557,7 +8949,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8740,7 +9136,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8801,7 +9201,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8862,7 +9266,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8923,7 +9331,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8984,7 +9396,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9167,7 +9583,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9228,7 +9648,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9289,7 +9713,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9411,7 +9839,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9472,7 +9904,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9533,7 +9969,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9594,7 +10034,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9655,7 +10099,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9716,7 +10164,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9777,7 +10229,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9838,7 +10294,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9899,7 +10359,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9960,7 +10424,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10021,7 +10489,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10082,7 +10554,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10204,7 +10680,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10326,7 +10806,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10387,7 +10871,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10448,7 +10936,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10509,7 +11001,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10570,7 +11066,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10692,7 +11192,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10753,7 +11257,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10875,7 +11383,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10936,7 +11448,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10997,7 +11513,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11058,7 +11578,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11119,7 +11643,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11180,7 +11708,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11241,7 +11773,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11363,7 +11899,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11424,7 +11964,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11485,7 +12029,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11546,7 +12094,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11607,7 +12159,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11668,7 +12224,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11729,7 +12289,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11790,7 +12354,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11851,7 +12419,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11912,7 +12484,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11973,7 +12549,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12034,7 +12614,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12217,7 +12801,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12278,7 +12866,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12339,7 +12931,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12400,7 +12996,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12461,7 +13061,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12522,7 +13126,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12827,7 +13435,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12888,7 +13500,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13010,7 +13626,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13071,7 +13691,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13132,7 +13756,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13376,7 +14004,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13742,7 +14374,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13803,7 +14439,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13864,7 +14504,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13925,7 +14569,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14230,7 +14878,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14291,7 +14943,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14352,7 +15008,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14413,7 +15073,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14474,7 +15138,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
